--- a/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-correction.xlsx
@@ -41,7 +41,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">用 cdiv 计算 tile 数量</t>
+          <t xml:space="preserve">用向上整除计算 tile 数量</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -61,20 +61,21 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：cdiv 已经执行向上整除，不能先用 // 丢掉余数。
-[T#B,!c47f17#边界]：group 数量同理使用 cdiv(num_pid_m, GROUP_SIZE_M)。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先做 // 会丢掉余数，向上整除必须接收原始长度和块长。
+• [T#B#例子]：M=257、块长64，需要5块；只取整数商会漏掉最后1个元素。
+[T#B,!c47f17#边界]：长度与块长取正整数；group 数量同理使用 cdiv(num_pid_m, GROUP_SIZE_M)。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">计算尾组的标量最小值</t>
+          <t xml:space="preserve">比较两个标量的最小值</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 kernel 中比较剩余 pid_m 与 GROUP_SIZE_M</t>
+          <t xml:space="preserve">Triton 3.7.1 中计算尾组实际大小</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -89,9 +90,9 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：tl.min 是 reduction API；tl.minimum 才执行 elementwise minimum。
-• [T#B#报错原因]：tl.min 的第二个位置参数会被解释为 reduction axis。
-[T#B,!c47f17#边界]：这是本课 Triton 3.7.1 环境的 API 快照。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：tl.minimum 做逐元素最小值；tl.min 沿某个轴归约。
+• [T#B#根因]：tl.min 的第二个位置参数是归约轴，不能把它当作第二个待比较的标量。
+[T#B,!c47f17#边界]：这条记录绑定本课 Triton 3.7.1 API；并非说 tl.min 本身无效。</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-correction.xlsx
@@ -41,17 +41,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">用向上整除计算 tile 数量</t>
+          <t xml:space="preserve">计算分块矩阵乘法覆盖 M 个输出行所需的 tile 数量。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">M 不能被 BLOCK_SIZE_M 整除</t>
+          <t xml:space="preserve">每个输出 tile 覆盖 BLOCK_SIZE_M 行；M 不能被块长整除，因此最后不足一块的行也必须有 program 处理。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdiv(M, BLOCK_SIZE_M)</t>
+          <t xml:space="preserve">使用 cdiv(M, BLOCK_SIZE_M)，把原始总行数和每块行数作为两个参数传入。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -61,26 +61,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先做 // 会丢掉余数，向上整除必须接收原始长度和块长。
-• [T#B#例子]：M=257、块长64，需要5块；只取整数商会漏掉最后1个元素。
-[T#B,!c47f17#边界]：长度与块长取正整数；group 数量同理使用 cdiv(num_pid_m, GROUP_SIZE_M)。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：向上整除的目标是把不足一块的剩余行也计为一块，不能先用整数除法丢掉余数。
+• [T#B#通用含义]：所需块数为 ceil(M/BLOCK_SIZE_M)。cdiv 接收原始长度与块长，而不是接收已经算过的整数商。
+• [T#B#具体例子]：M=257、BLOCK_SIZE_M=64 时，前四块只覆盖 256 行，还需要第五块处理最后一行。257//64 等于 4，已经丢失了这个尾部信息。
+[T#B,!c47f17#边界]：长度和块长取正整数。若进一步计算分组数量，同理应写 cdiv(num_pid_m,GROUP_SIZE_M)，不能先整除。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比较两个标量的最小值</t>
+          <t xml:space="preserve">在 Triton kernel 内求两个标量的较小值，以确定输出 tile 尾组的实际组高。</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 中计算尾组实际大小</t>
+          <t xml:space="preserve">Triton 3.7.1 中，x 是设定的 GROUP_SIZE_M，y 是尚未覆盖的输出 tile 行数；此处需要在 x、y 两个数之间取最小值。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tl.minimum(x, y)</t>
+          <t xml:space="preserve">使用 tl.minimum(x, y) 比较这两个值。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -90,9 +91,10 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：tl.minimum 做逐元素最小值；tl.min 沿某个轴归约。
-• [T#B#根因]：tl.min 的第二个位置参数是归约轴，不能把它当作第二个待比较的标量。
-[T#B,!c47f17#边界]：这条记录绑定本课 Triton 3.7.1 API；并非说 tl.min 本身无效。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：tl.minimum 比较两个输入的对应元素；tl.min 则对一个输入沿指定轴做归约，两者承担的任务不同。
+• [T#B#错误根因]：把 tl.min(x,y) 当成双参数取最小值时，y 会被解释为归约轴，而不是第二个待比较的标量，因此不符合尾组大小计算的需求。
+• [T#B#回到任务]：例如设定组高 x=2、剩余行数 y=1，目标是得到实际组高 1；tl.minimum(x,y) 正好表达这个比较。
+[T#B,!c47f17#边界]：这里绑定 Triton 3.7.1 的 API。需要沿张量的某个轴求最小值时，tl.min 仍然是相应的归约操作。</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-correction.xlsx
@@ -41,60 +41,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">计算分块矩阵乘法覆盖 M 个输出行所需的 tile 数量。</t>
+          <t xml:space="preserve">在 Triton kernel 里计算输出 tile 尾组的实际组高：在两个标量之间取较小值。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">每个输出 tile 覆盖 BLOCK_SIZE_M 行；M 不能被块长整除，因此最后不足一块的行也必须有 program 处理。</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中：num_pid_m 是输出 tile 的总行数，first_pid_m 是当前组的起始 tile 行号，GROUP_SIZE_M 是设定组高；实际组高取 num_pid_m − first_pid_m 与 GROUP_SIZE_M 中较小的一个。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">使用 cdiv(M, BLOCK_SIZE_M)，把原始总行数和每块行数作为两个参数传入。</t>
+          <t xml:space="preserve">tl.minimum(num_pid_m - first_pid_m, GROUP_SIZE_M)，或教程使用的 Python 内建 min(num_pid_m - first_pid_m, GROUP_SIZE_M)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cdiv(M // BLOCK_SIZE_M)</t>
+          <t xml:space="preserve">this_group_size_m = tl.min(num_pid_m - first_pid_m, GROUP_SIZE_M)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：向上整除的目标是把不足一块的剩余行也计为一块，不能先用整数除法丢掉余数。
-• [T#B#通用含义]：所需块数为 ceil(M/BLOCK_SIZE_M)。cdiv 接收原始长度与块长，而不是接收已经算过的整数商。
-• [T#B#具体例子]：M=257、BLOCK_SIZE_M=64 时，前四块只覆盖 256 行，还需要第五块处理最后一行。257//64 等于 4，已经丢失了这个尾部信息。
-[T#B,!c47f17#边界]：长度和块长取正整数。若进一步计算分组数量，同理应写 cdiv(num_pid_m,GROUP_SIZE_M)，不能先整除。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在把归约 API tl.min 当成两数取小：它的第二个位置参数是归约轴，GROUP_SIZE_M 被当成了轴号，于是编译阶段就报 invalid axis。
+• [T#B#两类 API]：tl.minimum 与 JIT 中的内建 min 都表示两个值取小，这里比较的是两个标量；tl.min 则把一个张量沿指定轴归约。
+• [T#B#诊断线索]：第一版的数值用例全部停在编译阶段，报错指向 axis 而不是数值结果，这正是参数被当成归约轴的信号。
+[T#B,!c47f17#边界]：需要沿张量的某个轴求最小值时，tl.min 仍是对应的归约操作；以上 API 语义按 Triton 3.7.1 核对。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">在 Triton kernel 内求两个标量的较小值，以确定输出 tile 尾组的实际组高。</t>
+          <t xml:space="preserve">根据 ABBA 顺序的 benchmark 读数，给出 GROUP_SIZE_M=1 与 2 的性能结论。</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 中，x 是设定的 GROUP_SIZE_M，y 是尚未覆盖的输出 tile 行数；此处需要在 x、y 两个数之间取最小值。</t>
+          <t xml:space="preserve">RTX 5090 上的 matmul，M=N=K=4096，固定 64×64×32 block、4 warps、3 stages 和同一输入，只改变 GROUP_SIZE_M；按 1→2→2→1 的顺序测得 median 0.6687、0.6902、0.6943、0.6975 ms（group 1 首末两次相差约 4%）。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">使用 tl.minimum(x, y) 比较这两个值。</t>
+          <t xml:space="preserve">只能说：在这台 RTX 5090、该 shape、固定 launch 配置和本次方法下，GROUP_SIZE_M 的影响无法与约 4% 的运行状态漂移稳定分离；既不支持 group 2 更快，也不支持 group 1 更快。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tl.min(x, y)</t>
+          <t xml:space="preserve">在当前环境和固定配置上，对性能影响较小</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：tl.minimum 比较两个输入的对应元素；tl.min 则对一个输入沿指定轴做归约，两者承担的任务不同。
-• [T#B#错误根因]：把 tl.min(x,y) 当成双参数取最小值时，y 会被解释为归约轴，而不是第二个待比较的标量，因此不符合尾组大小计算的需求。
-• [T#B#回到任务]：例如设定组高 x=2、剩余行数 y=1，目标是得到实际组高 1；tl.minimum(x,y) 正好表达这个比较。
-[T#B,!c47f17#边界]：这里绑定 Triton 3.7.1 的 API。需要沿张量的某个轴求最小值时，tl.min 仍然是相应的归约操作。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在把“分不出差异”升级成“差异很小”：配置差异与约 4% 的运行漂移混在一起时，看不清差异可能是噪声太大，而不是差异本身小。
+• [T#B#读数为何分不开]：前半程 group 1 更快、后半程 group 2 略快，两对比较的方向相反；同一个 group 1 首末两次就差约 4%，配置带来的差异淹没在漂移里。
+• [T#B#能下的结论]：这组读数既不支持 group 2 更快，也不能反过来断言 group 1 更快；结论只限于本机、该 shape、固定配置和本次测量方法。
+[T#B,!c47f17#边界]：这次“分不出来”不能外推成 grouped ordering 没有收益；换设备、shape、分组大小或测量方法都要重新测量。</t>
         </is>
       </c>
     </row>
